--- a/analytikI/platy.xlsx
+++ b/analytikI/platy.xlsx
@@ -136,7 +136,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Platy zamestnancov v roku 2026</a:t>
+              <a:t>Plat zamestnancov</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -156,12 +156,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Zamestnanci'!$A$2:$A$6</f>
+              <f>'Zamestnanci'!$C$2:$C$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Zamestnanci'!$B$2:$B$6</f>
+              <f>'Zamestnanci'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -235,9 +235,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -547,69 +547,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Priezvisko</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Plat</t>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>salary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Doe</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Johnson</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Williams</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>70000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Brown</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>250000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>priemer</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>AVERAGE(D2:D6)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
